--- a/Zerde_Ulttyq_oiyndar/Zertteu_kestesi.xlsx
+++ b/Zerde_Ulttyq_oiyndar/Zertteu_kestesi.xlsx
@@ -1332,7 +1332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1383,8 +1383,16 @@
           <t>Ертегі</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="7" t="n"/>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік [Мәтін] : қазақтың көне ертегілері (жаңартылған нұсқа) / М. Байбеков О. Байбеков ... – Тараз : Сенім, 2019</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -1400,8 +1408,16 @@
           <t>Ертегі</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="7" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>https://adebiportal.kz/kz/balaqai/view/kerqula-atty-kendebai__126</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1417,8 +1433,16 @@
           <t>Ертегі</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="7" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Алтын сақа – Алматы, 1972.</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1426,7 +1450,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Аяз би</t>
+          <t>Күн астындағы Күнікей қыз</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1434,8 +1458,16 @@
           <t>Ертегі</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="7" t="n"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>https://bilim-all.kz/article/263</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1443,16 +1475,24 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Жиренше шешен</t>
+          <t>Алпамыс батыр</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Ертегі</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="7" t="n"/>
+          <t>Жыр</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Алпамыс батыр : эпостың баяны / ... – Астана : Фолиант, 2012.</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1460,16 +1500,24 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Алдар Көсе әңгімелері</t>
+          <t>Қобыланды батыр</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Ертегі</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="7" t="n"/>
+          <t>Жыр</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Қобыланды батыр [Мәтін] / ... – Алматы : Mazmundama, 2022</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1477,16 +1525,24 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Қаңбақ шал</t>
+          <t>Ер Тарғын</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Ертегі</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="7" t="n"/>
+          <t>Жыр</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Ер Тарғын [Мәтін] : батырлар жыры / ... – Астана : Алматыкітап, 2007.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1494,16 +1550,24 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Күн астындағы Күнікей қыз</t>
+          <t>Қамбар батыр</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Ертегі</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="7" t="n"/>
+          <t>Жыр</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>https://bilim-all.kz/olen/4898-qambar-batyr</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1511,7 +1575,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Алпамыс батыр</t>
+          <t>Қыз Жібек</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1519,8 +1583,16 @@
           <t>Жыр</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="7" t="n"/>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Қыз Жібек [Мәтін] : Лиро-эпостық поэма  – Алматы : Мектеп, 2003.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1528,7 +1600,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Қобыланды батыр</t>
+          <t>Қозы Көрпеш – Баян сұлу</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1536,8 +1608,16 @@
           <t>Жыр</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="7" t="n"/>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Қозы Көрпеш - Баян Сұлу [Мәтін] : лиро-эпостық поэма : М. Ж. Көпейұлы нұсқасы / ... – Алматы : Мектеп, 2006</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1545,7 +1625,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Ер Тарғын</t>
+          <t>Айман – Шолпан</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1553,80 +1633,20 @@
           <t>Жыр</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Қамбар батыр</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Жыр</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Қыз Жібек</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Жыр</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Қозы Көрпеш – Баян сұлу</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Жыр</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Айман – Шолпан</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Жыр</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="7" t="n"/>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Айман-Шолпан [Мәтін] : Қазақ эпосы / ; Қазақ ССР Ғылым Академиясы, Тіл және әдебиет институты ; [баспаға даярлаған Ы. Т. Дүйсенбаев]... – Алматы : Қазақ ССР Ғылым Академиясының Баспасы, 1957</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>иә</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2 E3 E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2 E3 E4 E5 E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"иә,жоқ"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1718,336 +1738,770 @@
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="n"/>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Алпамыс батыр</t>
+        </is>
+      </c>
       <c r="C2" s="4">
-        <f>IFERROR(VLOOKUP(B2,Шығармалар!$B$2:$C$16,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D2" s="6" t="n"/>
+        <f>IFERROR(VLOOKUP(B2,Шығармалар!$B$2:$C$12,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Жамбы ату</t>
+        </is>
+      </c>
       <c r="E2" s="6" t="n"/>
       <c r="F2" s="5">
         <f>IFERROR(VLOOKUP(D2,Ойындар!$B$2:$C$14,2,0),"")</f>
         <v/>
       </c>
-      <c r="G2" s="6" t="n"/>
-      <c r="H2" s="6" t="n"/>
-      <c r="I2" s="7" t="n"/>
-      <c r="J2" s="6" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Алпамыс, Ұлтан</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Алпамыс бөгелген жоқ, садақты шірене тартып, жамбыны сыңғыр
+еткізіп атып түсірді.</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Ұлтан ханға барсам деп,
+Жамбыны атып алсам деп,
+Көңілі тасып, құлшынды.
+Анасымен көрісіп,
+Көздің жасын төгісіп,                                         Енді атына мінеді,
+Жамбыға қарай жүреді.                           «Диуана да келді!»— деп,
+Мазақ қып Ұлтан күледі.
+Атайын деп оқталып,
+Төсіне садақ тіреді.
+Атып тастап жамбыны,
+Ұлтанға жетіп келеді.</t>
+        </is>
+      </c>
       <c r="K2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="n"/>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Алпамыс батыр</t>
+        </is>
+      </c>
       <c r="C3" s="4">
-        <f>IFERROR(VLOOKUP(B3,Шығармалар!$B$2:$C$16,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D3" s="6" t="n"/>
+        <f>IFERROR(VLOOKUP(B3,Шығармалар!$B$2:$C$12,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Көкпар</t>
+        </is>
+      </c>
       <c r="E3" s="6" t="n"/>
       <c r="F3" s="5">
         <f>IFERROR(VLOOKUP(D3,Ойындар!$B$2:$C$14,2,0),"")</f>
         <v/>
       </c>
-      <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
-      <c r="I3" s="7" t="n"/>
-      <c r="J3" s="6" t="n"/>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Жәдігер, Гүлбаршын</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Жәдігер ойлады: «Менің көкпар шабатын заманым болса, өстіп жүрем бе, бұл көкпарды Қарлығаш апама апарып берейін, жігіттерге асып берсін!» — деп, мойнында кісен, аяғында шынжыр, құнан атына сүйретіп ауылға алып барды.</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Қ</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Гүлбаршынның алдына
+Көкпар әкеп тастады,
+Өңгеріп серке даладан.</t>
+        </is>
+      </c>
       <c r="K3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Қобыланды батыр</t>
+        </is>
+      </c>
       <c r="C4" s="4">
-        <f>IFERROR(VLOOKUP(B4,Шығармалар!$B$2:$C$16,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D4" s="6" t="n"/>
+        <f>IFERROR(VLOOKUP(B4,Шығармалар!$B$2:$C$12,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Бәйге</t>
+        </is>
+      </c>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="5">
         <f>IFERROR(VLOOKUP(D4,Ойындар!$B$2:$C$14,2,0),"")</f>
         <v/>
       </c>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="7" t="n"/>
-      <c r="J4" s="6" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Құртқа, Қобыланды</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Бәйгеден келген аттар туралы айтылады; Құртқа Қобыландының сапарға аттанатынын біліп, Тайбурылға алтын ер салып дайындайды.</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Қ</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Бәйгеден келген кѳк дѳнен,
+Түнімен ұйқы кѳрмеген
+Қобландыдай батырдың
+Тоқтамасын білген соң,
+Тайбурылдың үстіне
+Алтыннан тұрман ер салып,
+Аз ғана азық, жем салып,
+Ақ орданың алдынан
+Ѳткізді Құртқа кѳлденең</t>
+        </is>
+      </c>
       <c r="K4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="n"/>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C5" s="4">
-        <f>IFERROR(VLOOKUP(B5,Шығармалар!$B$2:$C$16,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D5" s="6" t="n"/>
+        <f>IFERROR(VLOOKUP(B5,Шығармалар!$B$2:$C$12,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Бәйге</t>
+        </is>
+      </c>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="5">
         <f>IFERROR(VLOOKUP(D5,Ойындар!$B$2:$C$14,2,0),"")</f>
         <v/>
       </c>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="6" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік, Темір хан</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Темір хан ат бәйгесін өткізіп, бар жүйрігін қосады; Төстік Шалқұйрықты бәйгеге дайындайды, аттар бір жұмалық жерден шабады.</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Қ</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Бұдан жеңілген соң Темір хан ат шабысына шығады. Өзінің бар жүйрігін бәйгеге қосады. Ер Төстік Шалқұйрықты даярлайды. Қарақшының түбіне келген соң, Шалқұйрыққа тіл бітеді: - Егер атты өте алысқа айдаса, менің шабысым өте жылдам болады. Үш күн шапсам, бүйірім қызып, өзімді тоқтатуға шамам келмей, кетіп қалуым мүмкін. Мен келе жатқанда алдымнан арқан керіп қой. Арқан үш қабат болсын, бір қабаты кендірден болсын. Үш қабат арқанның үшеуі де үзілсе, мен саған жоқпын, ағынымды тоқтата алмай кеткенім, үшеуі де үзілмесе, мен жығылып өлемін, онда да саған жоқпын. Егер арқан жартылай үзілсе, мен тоқтаймын, жығылып қалсам да, жаным қайтадан кіреді, күдер үзбе, - дейді. "Ер Төстіктің жалғыз шолағы бір жерде зарығып өліп қалсын!" - деп, Темір хан атты бір жұмалық жерге айдатады.Бір жеті өткен соң, бәйге аттары қайтып оралады. Темір хан мен Кеще хан балуан және ат бәйгесінен жеңіліп, не қыларын білмей, сасады. "Енді жаяу жарыс салып көрейік", - дейді.</t>
+        </is>
+      </c>
       <c r="K5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C6" s="4">
-        <f>IFERROR(VLOOKUP(B6,Шығармалар!$B$2:$C$16,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D6" s="6" t="n"/>
+        <f>IFERROR(VLOOKUP(B6,Шығармалар!$B$2:$C$12,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Күрес</t>
+        </is>
+      </c>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="5">
         <f>IFERROR(VLOOKUP(D6,Ойындар!$B$2:$C$14,2,0),"")</f>
         <v/>
       </c>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="6" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Таусоғар, Темір хан</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Балуан күресінде жер астының алыптары Таусоғарға шақ келмейді, ол тауды көтеріп, күшін көрсетеді.</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Балуан күресі басталады. Таусоғарға балуан шақ келмейді. Жер астының алыптарының бәрі жығылып бітеді. Күресуге кісі шықпаған соң, Таусоғар бір тауды көтеріп алып, жұртқа күшін көрсетеді. Темір хан мен Кеще хан қатты сасып:
+     -Тауды біз жаққа қоя көрмесін! - деп Төстікке жалынады.</t>
+        </is>
+      </c>
       <c r="K6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="n"/>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
       <c r="C7" s="4">
-        <f>IFERROR(VLOOKUP(B7,Шығармалар!$B$2:$C$16,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D7" s="6" t="n"/>
+        <f>IFERROR(VLOOKUP(B7,Шығармалар!$B$2:$C$12,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Асық</t>
+        </is>
+      </c>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="5">
         <f>IFERROR(VLOOKUP(D7,Ойындар!$B$2:$C$14,2,0),"")</f>
         <v/>
       </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Ер Төстік</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Төстік асық ойнап жүріп, кемпірдің баласын ұрып қалады; кемпірдің ызасынан кейін Төстік ағаларын іздеп жолға шығады.</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Тағы бір күні Төстік асық ойнап жүріп, әлгі кемпірдің жалғыз баласын жұдырығымен қойып жіберсе, бала талып қалады.</t>
+        </is>
+      </c>
       <c r="K7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Керқұла атты Кендебай</t>
+        </is>
+      </c>
       <c r="C8" s="4">
-        <f>IFERROR(VLOOKUP(B8,Шығармалар!$B$2:$C$16,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D8" s="6" t="n"/>
+        <f>IFERROR(VLOOKUP(B8,Шығармалар!$B$2:$C$12,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Күрес</t>
+        </is>
+      </c>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="5">
         <f>IFERROR(VLOOKUP(D8,Ойындар!$B$2:$C$14,2,0),"")</f>
         <v/>
       </c>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="6" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Кендебай</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Кендебай ерекше күшті болып өседі: күрескенін жыға береді, құдыққа құлаған түйелерді жалғыз тартып шығарады.</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Сондай күшті болыпты, алысқанын алып ұра беріпті, күрескенін жыға беріпті, шыңырау құдыққа құлаған атандарды жалғыз тартып шығара беріпті.</t>
+        </is>
+      </c>
       <c r="K8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="n"/>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Алтын сақа</t>
+        </is>
+      </c>
       <c r="C9" s="4">
-        <f>IFERROR(VLOOKUP(B9,Шығармалар!$B$2:$C$16,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D9" s="6" t="n"/>
+        <f>IFERROR(VLOOKUP(B9,Шығармалар!$B$2:$C$12,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Асық</t>
+        </is>
+      </c>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="5">
         <f>IFERROR(VLOOKUP(D9,Ойындар!$B$2:$C$14,2,0),"")</f>
         <v/>
       </c>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Бала, жалмауыз кемпір</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Ауыл көшкенде баланың алтын сақасы жұртта қалады; бала оны алуға қайтып барып, жалмауыз кемпірге кездеседі.</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Сонымен бай жалмауыз кемпірге уәдесін беріп, жылқыларын айдап, кетіп қалады. Ертеңінде көшеді, жалғыз баласының алтын сақасын ұмыттырып, жұртқа тастап кетеді. Ауыл жаңа қонысқа көшіп барады. Асық ойнайын десе, сақасы жоқ, бала алтын сақасын жоқтап, жылайды. Жұртқа келсе, алтын сақасы ошақ басындағы тезек түбінде жатыр екен. Сақа жанында бір кемпір отыр екен. Бала кемпірге:
+— Шеше, анау жатқан сақамды алып берші! – дейді.
+Сонда кемпір:
+— Шырағым, өзің түсіп ал. Кәріліктен отырсам -тұра алмаймын, тұрсам - отыра алмаймын, – дейді.</t>
+        </is>
+      </c>
       <c r="K9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="n"/>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Қыз Жібек</t>
+        </is>
+      </c>
       <c r="C10" s="4">
-        <f>IFERROR(VLOOKUP(B10,Шығармалар!$B$2:$C$16,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D10" s="6" t="n"/>
+        <f>IFERROR(VLOOKUP(B10,Шығармалар!$B$2:$C$12,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Асық</t>
+        </is>
+      </c>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="5">
         <f>IFERROR(VLOOKUP(D10,Ойындар!$B$2:$C$14,2,0),"")</f>
         <v/>
       </c>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Жастар</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Жастардың қызықты өмірі суреттеледі: олар тай-құлындай тебісіп, асық ойнап алысады.</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Көп қызыққа батысқан, Тай құлындай тебіскен, Асық ойнап алысқан.</t>
+        </is>
+      </c>
       <c r="K10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="n"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Күн астындағы Күнікей қыз</t>
+        </is>
+      </c>
       <c r="C11" s="4">
-        <f>IFERROR(VLOOKUP(B11,Шығармалар!$B$2:$C$16,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
+        <f>IFERROR(VLOOKUP(B11,Шығармалар!$B$2:$C$12,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Басқа</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Жаяу бәйге</t>
+        </is>
+      </c>
       <c r="F11" s="5">
         <f>IFERROR(VLOOKUP(D11,Ойындар!$B$2:$C$14,2,0),"")</f>
         <v/>
       </c>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Бала, мыстан кемпір, хан</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Хан сөзінен танып, қызын жаяу бәйгеде озған адамға беретінін айтады; ханның жағынан жүйрік мыстан кемпір шығады.</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Бірақ, хан сөзінен танып, бұл жолы қызын бермей:
+— Енді жаяу бәйгеден озып келгенге беремін, – дейді. Жаяу бәйгеге ханның елінен бір жүйрік мыстан кемпір шығады.</t>
+        </is>
+      </c>
       <c r="K11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="n"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Күн астындағы Күнікей қыз</t>
+        </is>
+      </c>
       <c r="C12" s="4">
-        <f>IFERROR(VLOOKUP(B12,Шығармалар!$B$2:$C$16,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D12" s="6" t="n"/>
+        <f>IFERROR(VLOOKUP(B12,Шығармалар!$B$2:$C$12,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Күрес</t>
+        </is>
+      </c>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="5">
         <f>IFERROR(VLOOKUP(D12,Ойындар!$B$2:$C$14,2,0),"")</f>
         <v/>
       </c>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Дәу, өгіз балуан, хан</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Хан қызын күресте жеңгенге беремін дейді; баланың жолдасы – екі қолына екі тау ұстаған дәу – ханның балуанын жығады.</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>С</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Хан ертеңіне, ел-жұртын жиып, балуан күрестіреді. Осы топта кімде-кім күресіп жығып, күші асса, қызымды соған беремін, – дейді. Ханның елі жағынан бір өгіз балуан шығады. Бала жағынан екі қолына екі тау ұстап жүруші дәу шығады. Екі балуан күресіп, дәу жығып кетеді.</t>
+        </is>
+      </c>
       <c r="K12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="n"/>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Ер Тарғын</t>
+        </is>
+      </c>
       <c r="C13" s="4">
-        <f>IFERROR(VLOOKUP(B13,Шығармалар!$B$2:$C$16,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D13" s="6" t="n"/>
+        <f>IFERROR(VLOOKUP(B13,Шығармалар!$B$2:$C$12,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Бәйге</t>
+        </is>
+      </c>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="5">
         <f>IFERROR(VLOOKUP(D13,Ойындар!$B$2:$C$14,2,0),"")</f>
         <v/>
       </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Ер Тарғын</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Тарғын Тарлан атымен жауға шабуды «Тарлан бәйгесі» деп атайды – бәйге бейнесі батырдың ерлігін көрсетеді.</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Қ</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Кебеже қарын, кең құрсақ,
+Құлжа мойын төгерек,
+Ұмтыла шапқан Тарланым,
+Алты мыңдай кісі екен,
+Тіл жіберсең саған серт!
+Сен желігіп жүргенде,
+Таяна шапса маған серт!
+Тауыса шапса бұ жауды,
+Сонда бітер Тарлан бәйгесі</t>
+        </is>
+      </c>
       <c r="K13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="n"/>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Қамбар батыр</t>
+        </is>
+      </c>
       <c r="C14" s="4">
-        <f>IFERROR(VLOOKUP(B14,Шығармалар!$B$2:$C$16,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D14" s="6" t="n"/>
+        <f>IFERROR(VLOOKUP(B14,Шығармалар!$B$2:$C$12,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Аударыспақ</t>
+        </is>
+      </c>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="5">
         <f>IFERROR(VLOOKUP(D14,Ойындар!$B$2:$C$14,2,0),"")</f>
         <v/>
       </c>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Қараман, бектер</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Қараман бастаған бектер кернейлетіп қаладан шығып, ат үстінде аударысып ойнайды.</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Қ</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Қараман шықты қаладан,
+Кернейлері бақылдап,
+Байрақтар тулап көтерген,
+Алтыннан қалқан жарқылдап,
+Сыбызғы, сырнай шақылдап,
+Мінгендері дәл бедеу,
+Келеді бектер дабылдап.
+Аударысып ойнайды
+Буыршындай тақымдап;</t>
+        </is>
+      </c>
       <c r="K14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="n"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Қозы Көрпеш – Баян сұлу</t>
+        </is>
+      </c>
       <c r="C15" s="4">
-        <f>IFERROR(VLOOKUP(B15,Шығармалар!$B$2:$C$16,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="6" t="n"/>
+        <f>IFERROR(VLOOKUP(B15,Шығармалар!$B$2:$C$12,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Аударыспақ</t>
+        </is>
+      </c>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="5">
         <f>IFERROR(VLOOKUP(D15,Ойындар!$B$2:$C$14,2,0),"")</f>
         <v/>
       </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Қозы Көрпеш</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Қозы жылқы бағып жүріп, тоқсан құлмен аударыспақ ойнайды және бәрін аттан аударып түсіреді – оның алып күші көрінеді.</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Қарабай оны жақсы көріп, жылқы бағуға жұмсайды. Қозы алғашқыда Қодармен әзілдесіп, кейде ойнап, ат үстінен жұлып алып жүреді. Кейде тоқсан құлмен аударыспақ ойнап, оларды тегісімен топырлатып жүреді. Халық ақындары бұл жерде Қозы Көрпешті жойқын алып түрінде суреттеп, оның жеңбейтін адамы жоқ деп сипаттайды.</t>
+        </is>
+      </c>
       <c r="K15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="n"/>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Қозы Көрпеш – Баян сұлу</t>
+        </is>
+      </c>
       <c r="C16" s="4">
-        <f>IFERROR(VLOOKUP(B16,Шығармалар!$B$2:$C$16,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="6" t="n"/>
+        <f>IFERROR(VLOOKUP(B16,Шығармалар!$B$2:$C$12,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Асық</t>
+        </is>
+      </c>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="5">
         <f>IFERROR(VLOOKUP(D16,Ойындар!$B$2:$C$14,2,0),"")</f>
         <v/>
       </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Қозы Көрпеш, тазша бала</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Қозы бала күнін асық ойнап өткізеді; тазша баланың сақасын тартып алғанда, «жарыңды іздеп тапсайшы» деген сөз естиді.</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Б</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Әкесінен жетім қалған Қозы Көрпеш ақылды анасы мен кемеңгер ағаларының қолында еркін өседі. Бала күнін бірыңғай асық ойнаумен өткізеді.Тазша баланың сақасын тартып алып, оның аузынан: «Менің сақамды тартып алғанша, жарыңды іздеп тапсайшы» деген сөз естиді.</t>
+        </is>
+      </c>
       <c r="K16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="n"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Айман – Шолпан</t>
+        </is>
+      </c>
       <c r="C17" s="4">
-        <f>IFERROR(VLOOKUP(B17,Шығармалар!$B$2:$C$16,2,0),"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="6" t="n"/>
+        <f>IFERROR(VLOOKUP(B17,Шығармалар!$B$2:$C$12,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Бәйге</t>
+        </is>
+      </c>
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="5">
         <f>IFERROR(VLOOKUP(D17,Ойындар!$B$2:$C$14,2,0),"")</f>
         <v/>
       </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Басыбар</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Басыбар бәйгеге ат жөнелтіп, қайта келетінін айтады – бәйге ас пен той дайындығының бөлігі ретінде аталады.</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Қ</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Басыбар: Тәйт, жоғал, ондайынды жолымнан ал
+былай! Күмілжімей, тек көмейің күлкілдемей сертінде қал
+жалтақтамай. Байлауым сол, кәзір бәйгеге ат жөнелтіп қайта
+мұнда келемін. Мыжымай қарсы алуға қамдана бер осы
+үйде!</t>
+        </is>
+      </c>
       <c r="K17" s="7" t="n"/>
     </row>
     <row r="18">
@@ -2056,7 +2510,7 @@
       </c>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="4">
-        <f>IFERROR(VLOOKUP(B18,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B18,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D18" s="6" t="n"/>
@@ -2077,7 +2531,7 @@
       </c>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="4">
-        <f>IFERROR(VLOOKUP(B19,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B19,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D19" s="6" t="n"/>
@@ -2098,7 +2552,7 @@
       </c>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="4">
-        <f>IFERROR(VLOOKUP(B20,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B20,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D20" s="6" t="n"/>
@@ -2119,7 +2573,7 @@
       </c>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="4">
-        <f>IFERROR(VLOOKUP(B21,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B21,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D21" s="6" t="n"/>
@@ -2140,7 +2594,7 @@
       </c>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="4">
-        <f>IFERROR(VLOOKUP(B22,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B22,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D22" s="6" t="n"/>
@@ -2161,7 +2615,7 @@
       </c>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="4">
-        <f>IFERROR(VLOOKUP(B23,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B23,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D23" s="6" t="n"/>
@@ -2182,7 +2636,7 @@
       </c>
       <c r="B24" s="6" t="n"/>
       <c r="C24" s="4">
-        <f>IFERROR(VLOOKUP(B24,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B24,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D24" s="6" t="n"/>
@@ -2203,7 +2657,7 @@
       </c>
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="4">
-        <f>IFERROR(VLOOKUP(B25,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B25,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D25" s="6" t="n"/>
@@ -2224,7 +2678,7 @@
       </c>
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="4">
-        <f>IFERROR(VLOOKUP(B26,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B26,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D26" s="6" t="n"/>
@@ -2245,7 +2699,7 @@
       </c>
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="4">
-        <f>IFERROR(VLOOKUP(B27,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B27,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D27" s="6" t="n"/>
@@ -2266,7 +2720,7 @@
       </c>
       <c r="B28" s="6" t="n"/>
       <c r="C28" s="4">
-        <f>IFERROR(VLOOKUP(B28,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B28,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D28" s="6" t="n"/>
@@ -2287,7 +2741,7 @@
       </c>
       <c r="B29" s="6" t="n"/>
       <c r="C29" s="4">
-        <f>IFERROR(VLOOKUP(B29,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B29,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D29" s="6" t="n"/>
@@ -2308,7 +2762,7 @@
       </c>
       <c r="B30" s="6" t="n"/>
       <c r="C30" s="4">
-        <f>IFERROR(VLOOKUP(B30,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B30,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D30" s="6" t="n"/>
@@ -2329,7 +2783,7 @@
       </c>
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="4">
-        <f>IFERROR(VLOOKUP(B31,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B31,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D31" s="6" t="n"/>
@@ -2350,7 +2804,7 @@
       </c>
       <c r="B32" s="6" t="n"/>
       <c r="C32" s="4">
-        <f>IFERROR(VLOOKUP(B32,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B32,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D32" s="6" t="n"/>
@@ -2371,7 +2825,7 @@
       </c>
       <c r="B33" s="6" t="n"/>
       <c r="C33" s="4">
-        <f>IFERROR(VLOOKUP(B33,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B33,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D33" s="6" t="n"/>
@@ -2392,7 +2846,7 @@
       </c>
       <c r="B34" s="6" t="n"/>
       <c r="C34" s="4">
-        <f>IFERROR(VLOOKUP(B34,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B34,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D34" s="6" t="n"/>
@@ -2413,7 +2867,7 @@
       </c>
       <c r="B35" s="6" t="n"/>
       <c r="C35" s="4">
-        <f>IFERROR(VLOOKUP(B35,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B35,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D35" s="6" t="n"/>
@@ -2434,7 +2888,7 @@
       </c>
       <c r="B36" s="6" t="n"/>
       <c r="C36" s="4">
-        <f>IFERROR(VLOOKUP(B36,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B36,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D36" s="6" t="n"/>
@@ -2455,7 +2909,7 @@
       </c>
       <c r="B37" s="6" t="n"/>
       <c r="C37" s="4">
-        <f>IFERROR(VLOOKUP(B37,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B37,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D37" s="6" t="n"/>
@@ -2476,7 +2930,7 @@
       </c>
       <c r="B38" s="6" t="n"/>
       <c r="C38" s="4">
-        <f>IFERROR(VLOOKUP(B38,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B38,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D38" s="6" t="n"/>
@@ -2497,7 +2951,7 @@
       </c>
       <c r="B39" s="6" t="n"/>
       <c r="C39" s="4">
-        <f>IFERROR(VLOOKUP(B39,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B39,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D39" s="6" t="n"/>
@@ -2518,7 +2972,7 @@
       </c>
       <c r="B40" s="6" t="n"/>
       <c r="C40" s="4">
-        <f>IFERROR(VLOOKUP(B40,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B40,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D40" s="6" t="n"/>
@@ -2539,7 +2993,7 @@
       </c>
       <c r="B41" s="6" t="n"/>
       <c r="C41" s="4">
-        <f>IFERROR(VLOOKUP(B41,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B41,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D41" s="6" t="n"/>
@@ -2560,7 +3014,7 @@
       </c>
       <c r="B42" s="6" t="n"/>
       <c r="C42" s="4">
-        <f>IFERROR(VLOOKUP(B42,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B42,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D42" s="6" t="n"/>
@@ -2581,7 +3035,7 @@
       </c>
       <c r="B43" s="6" t="n"/>
       <c r="C43" s="4">
-        <f>IFERROR(VLOOKUP(B43,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B43,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D43" s="6" t="n"/>
@@ -2602,7 +3056,7 @@
       </c>
       <c r="B44" s="6" t="n"/>
       <c r="C44" s="4">
-        <f>IFERROR(VLOOKUP(B44,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B44,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D44" s="6" t="n"/>
@@ -2623,7 +3077,7 @@
       </c>
       <c r="B45" s="6" t="n"/>
       <c r="C45" s="4">
-        <f>IFERROR(VLOOKUP(B45,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B45,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D45" s="6" t="n"/>
@@ -2644,7 +3098,7 @@
       </c>
       <c r="B46" s="6" t="n"/>
       <c r="C46" s="4">
-        <f>IFERROR(VLOOKUP(B46,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B46,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D46" s="6" t="n"/>
@@ -2665,7 +3119,7 @@
       </c>
       <c r="B47" s="6" t="n"/>
       <c r="C47" s="4">
-        <f>IFERROR(VLOOKUP(B47,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B47,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D47" s="6" t="n"/>
@@ -2686,7 +3140,7 @@
       </c>
       <c r="B48" s="6" t="n"/>
       <c r="C48" s="4">
-        <f>IFERROR(VLOOKUP(B48,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B48,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D48" s="6" t="n"/>
@@ -2707,7 +3161,7 @@
       </c>
       <c r="B49" s="6" t="n"/>
       <c r="C49" s="4">
-        <f>IFERROR(VLOOKUP(B49,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B49,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D49" s="6" t="n"/>
@@ -2728,7 +3182,7 @@
       </c>
       <c r="B50" s="6" t="n"/>
       <c r="C50" s="4">
-        <f>IFERROR(VLOOKUP(B50,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B50,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D50" s="6" t="n"/>
@@ -2749,7 +3203,7 @@
       </c>
       <c r="B51" s="6" t="n"/>
       <c r="C51" s="4">
-        <f>IFERROR(VLOOKUP(B51,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B51,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D51" s="6" t="n"/>
@@ -2770,7 +3224,7 @@
       </c>
       <c r="B52" s="6" t="n"/>
       <c r="C52" s="4">
-        <f>IFERROR(VLOOKUP(B52,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B52,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D52" s="6" t="n"/>
@@ -2791,7 +3245,7 @@
       </c>
       <c r="B53" s="6" t="n"/>
       <c r="C53" s="4">
-        <f>IFERROR(VLOOKUP(B53,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B53,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D53" s="6" t="n"/>
@@ -2812,7 +3266,7 @@
       </c>
       <c r="B54" s="6" t="n"/>
       <c r="C54" s="4">
-        <f>IFERROR(VLOOKUP(B54,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B54,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D54" s="6" t="n"/>
@@ -2833,7 +3287,7 @@
       </c>
       <c r="B55" s="6" t="n"/>
       <c r="C55" s="4">
-        <f>IFERROR(VLOOKUP(B55,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B55,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D55" s="6" t="n"/>
@@ -2854,7 +3308,7 @@
       </c>
       <c r="B56" s="6" t="n"/>
       <c r="C56" s="4">
-        <f>IFERROR(VLOOKUP(B56,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B56,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D56" s="6" t="n"/>
@@ -2875,7 +3329,7 @@
       </c>
       <c r="B57" s="6" t="n"/>
       <c r="C57" s="4">
-        <f>IFERROR(VLOOKUP(B57,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B57,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D57" s="6" t="n"/>
@@ -2896,7 +3350,7 @@
       </c>
       <c r="B58" s="6" t="n"/>
       <c r="C58" s="4">
-        <f>IFERROR(VLOOKUP(B58,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B58,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D58" s="6" t="n"/>
@@ -2917,7 +3371,7 @@
       </c>
       <c r="B59" s="6" t="n"/>
       <c r="C59" s="4">
-        <f>IFERROR(VLOOKUP(B59,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B59,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D59" s="6" t="n"/>
@@ -2938,7 +3392,7 @@
       </c>
       <c r="B60" s="6" t="n"/>
       <c r="C60" s="4">
-        <f>IFERROR(VLOOKUP(B60,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B60,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D60" s="6" t="n"/>
@@ -2959,7 +3413,7 @@
       </c>
       <c r="B61" s="6" t="n"/>
       <c r="C61" s="4">
-        <f>IFERROR(VLOOKUP(B61,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B61,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D61" s="6" t="n"/>
@@ -2980,7 +3434,7 @@
       </c>
       <c r="B62" s="6" t="n"/>
       <c r="C62" s="4">
-        <f>IFERROR(VLOOKUP(B62,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B62,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D62" s="6" t="n"/>
@@ -3001,7 +3455,7 @@
       </c>
       <c r="B63" s="6" t="n"/>
       <c r="C63" s="4">
-        <f>IFERROR(VLOOKUP(B63,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B63,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D63" s="6" t="n"/>
@@ -3022,7 +3476,7 @@
       </c>
       <c r="B64" s="6" t="n"/>
       <c r="C64" s="4">
-        <f>IFERROR(VLOOKUP(B64,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B64,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D64" s="6" t="n"/>
@@ -3043,7 +3497,7 @@
       </c>
       <c r="B65" s="6" t="n"/>
       <c r="C65" s="4">
-        <f>IFERROR(VLOOKUP(B65,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B65,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D65" s="6" t="n"/>
@@ -3064,7 +3518,7 @@
       </c>
       <c r="B66" s="6" t="n"/>
       <c r="C66" s="4">
-        <f>IFERROR(VLOOKUP(B66,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B66,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D66" s="6" t="n"/>
@@ -3085,7 +3539,7 @@
       </c>
       <c r="B67" s="6" t="n"/>
       <c r="C67" s="4">
-        <f>IFERROR(VLOOKUP(B67,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B67,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D67" s="6" t="n"/>
@@ -3106,7 +3560,7 @@
       </c>
       <c r="B68" s="6" t="n"/>
       <c r="C68" s="4">
-        <f>IFERROR(VLOOKUP(B68,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B68,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D68" s="6" t="n"/>
@@ -3127,7 +3581,7 @@
       </c>
       <c r="B69" s="6" t="n"/>
       <c r="C69" s="4">
-        <f>IFERROR(VLOOKUP(B69,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B69,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D69" s="6" t="n"/>
@@ -3148,7 +3602,7 @@
       </c>
       <c r="B70" s="6" t="n"/>
       <c r="C70" s="4">
-        <f>IFERROR(VLOOKUP(B70,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B70,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D70" s="6" t="n"/>
@@ -3169,7 +3623,7 @@
       </c>
       <c r="B71" s="6" t="n"/>
       <c r="C71" s="4">
-        <f>IFERROR(VLOOKUP(B71,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B71,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D71" s="6" t="n"/>
@@ -3190,7 +3644,7 @@
       </c>
       <c r="B72" s="6" t="n"/>
       <c r="C72" s="4">
-        <f>IFERROR(VLOOKUP(B72,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B72,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D72" s="6" t="n"/>
@@ -3211,7 +3665,7 @@
       </c>
       <c r="B73" s="6" t="n"/>
       <c r="C73" s="4">
-        <f>IFERROR(VLOOKUP(B73,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B73,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D73" s="6" t="n"/>
@@ -3232,7 +3686,7 @@
       </c>
       <c r="B74" s="6" t="n"/>
       <c r="C74" s="4">
-        <f>IFERROR(VLOOKUP(B74,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B74,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D74" s="6" t="n"/>
@@ -3253,7 +3707,7 @@
       </c>
       <c r="B75" s="6" t="n"/>
       <c r="C75" s="4">
-        <f>IFERROR(VLOOKUP(B75,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B75,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D75" s="6" t="n"/>
@@ -3274,7 +3728,7 @@
       </c>
       <c r="B76" s="6" t="n"/>
       <c r="C76" s="4">
-        <f>IFERROR(VLOOKUP(B76,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B76,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D76" s="6" t="n"/>
@@ -3295,7 +3749,7 @@
       </c>
       <c r="B77" s="6" t="n"/>
       <c r="C77" s="4">
-        <f>IFERROR(VLOOKUP(B77,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B77,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D77" s="6" t="n"/>
@@ -3316,7 +3770,7 @@
       </c>
       <c r="B78" s="6" t="n"/>
       <c r="C78" s="4">
-        <f>IFERROR(VLOOKUP(B78,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B78,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D78" s="6" t="n"/>
@@ -3337,7 +3791,7 @@
       </c>
       <c r="B79" s="6" t="n"/>
       <c r="C79" s="4">
-        <f>IFERROR(VLOOKUP(B79,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B79,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D79" s="6" t="n"/>
@@ -3358,7 +3812,7 @@
       </c>
       <c r="B80" s="6" t="n"/>
       <c r="C80" s="4">
-        <f>IFERROR(VLOOKUP(B80,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B80,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D80" s="6" t="n"/>
@@ -3379,7 +3833,7 @@
       </c>
       <c r="B81" s="6" t="n"/>
       <c r="C81" s="4">
-        <f>IFERROR(VLOOKUP(B81,Шығармалар!$B$2:$C$16,2,0),"")</f>
+        <f>IFERROR(VLOOKUP(B81,Шығармалар!$B$2:$C$12,2,0),"")</f>
         <v/>
       </c>
       <c r="D81" s="6" t="n"/>
@@ -3397,7 +3851,7 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="B2 B3 B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24 B25 B26 B27 B28 B29 B30 B31 B32 B33 B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 B53 B54 B55 B56 B57 B58 B59 B60 B61 B62 B63 B64 B65 B66 B67 B68 B69 B70 B71 B72 B73 B74 B75 B76 B77 B78 B79 B80 B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Шығармалар!$B$2:$B$16</formula1>
+      <formula1>=Шығармалар!$B$2:$B$12</formula1>
     </dataValidation>
     <dataValidation sqref="D2 D3 D4 D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 D52 D53 D54 D55 D56 D57 D58 D59 D60 D61 D62 D63 D64 D65 D66 D67 D68 D69 D70 D71 D72 D73 D74 D75 D76 D77 D78 D79 D80 D81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Ойындар!$B$2:$B$14</formula1>

--- a/Zerde_Ulttyq_oiyndar/Zertteu_kestesi.xlsx
+++ b/Zerde_Ulttyq_oiyndar/Zertteu_kestesi.xlsx
@@ -4040,31 +4040,81 @@
           <t>С01</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="7" t="n"/>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="n"/>
-      <c r="I2" s="7" t="n"/>
-      <c r="J2" s="7" t="n"/>
-      <c r="K2" s="7" t="n"/>
-      <c r="L2" s="7" t="n"/>
-      <c r="M2" s="7" t="n"/>
-      <c r="N2" s="7" t="n"/>
-      <c r="O2" s="7" t="n"/>
-      <c r="P2" s="7" t="n"/>
-      <c r="Q2" s="7" t="n"/>
-      <c r="R2" s="7" t="n"/>
-      <c r="S2" s="7" t="n"/>
-      <c r="T2" s="7" t="n"/>
-      <c r="U2" s="7" t="n"/>
-      <c r="V2" s="7" t="n"/>
-      <c r="W2" s="7" t="n"/>
-      <c r="X2" s="7" t="n"/>
-      <c r="Y2" s="7" t="n"/>
-      <c r="Z2" s="7" t="n"/>
+      <c r="B2" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z2" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -4072,31 +4122,81 @@
           <t>С02</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
-      <c r="I3" s="7" t="n"/>
-      <c r="J3" s="7" t="n"/>
-      <c r="K3" s="7" t="n"/>
-      <c r="L3" s="7" t="n"/>
-      <c r="M3" s="7" t="n"/>
-      <c r="N3" s="7" t="n"/>
-      <c r="O3" s="7" t="n"/>
-      <c r="P3" s="7" t="n"/>
-      <c r="Q3" s="7" t="n"/>
-      <c r="R3" s="7" t="n"/>
-      <c r="S3" s="7" t="n"/>
-      <c r="T3" s="7" t="n"/>
-      <c r="U3" s="7" t="n"/>
-      <c r="V3" s="7" t="n"/>
-      <c r="W3" s="7" t="n"/>
-      <c r="X3" s="7" t="n"/>
-      <c r="Y3" s="7" t="n"/>
-      <c r="Z3" s="7" t="n"/>
+      <c r="B3" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z3" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -4104,31 +4204,81 @@
           <t>С03</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
-      <c r="J4" s="7" t="n"/>
-      <c r="K4" s="7" t="n"/>
-      <c r="L4" s="7" t="n"/>
-      <c r="M4" s="7" t="n"/>
-      <c r="N4" s="7" t="n"/>
-      <c r="O4" s="7" t="n"/>
-      <c r="P4" s="7" t="n"/>
-      <c r="Q4" s="7" t="n"/>
-      <c r="R4" s="7" t="n"/>
-      <c r="S4" s="7" t="n"/>
-      <c r="T4" s="7" t="n"/>
-      <c r="U4" s="7" t="n"/>
-      <c r="V4" s="7" t="n"/>
-      <c r="W4" s="7" t="n"/>
-      <c r="X4" s="7" t="n"/>
-      <c r="Y4" s="7" t="n"/>
-      <c r="Z4" s="7" t="n"/>
+      <c r="B4" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z4" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -4136,31 +4286,81 @@
           <t>С04</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
-      <c r="K5" s="7" t="n"/>
-      <c r="L5" s="7" t="n"/>
-      <c r="M5" s="7" t="n"/>
-      <c r="N5" s="7" t="n"/>
-      <c r="O5" s="7" t="n"/>
-      <c r="P5" s="7" t="n"/>
-      <c r="Q5" s="7" t="n"/>
-      <c r="R5" s="7" t="n"/>
-      <c r="S5" s="7" t="n"/>
-      <c r="T5" s="7" t="n"/>
-      <c r="U5" s="7" t="n"/>
-      <c r="V5" s="7" t="n"/>
-      <c r="W5" s="7" t="n"/>
-      <c r="X5" s="7" t="n"/>
-      <c r="Y5" s="7" t="n"/>
-      <c r="Z5" s="7" t="n"/>
+      <c r="B5" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z5" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -4168,31 +4368,81 @@
           <t>С05</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="7" t="n"/>
-      <c r="N6" s="7" t="n"/>
-      <c r="O6" s="7" t="n"/>
-      <c r="P6" s="7" t="n"/>
-      <c r="Q6" s="7" t="n"/>
-      <c r="R6" s="7" t="n"/>
-      <c r="S6" s="7" t="n"/>
-      <c r="T6" s="7" t="n"/>
-      <c r="U6" s="7" t="n"/>
-      <c r="V6" s="7" t="n"/>
-      <c r="W6" s="7" t="n"/>
-      <c r="X6" s="7" t="n"/>
-      <c r="Y6" s="7" t="n"/>
-      <c r="Z6" s="7" t="n"/>
+      <c r="B6" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -4200,31 +4450,81 @@
           <t>С06</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="7" t="n"/>
-      <c r="L7" s="7" t="n"/>
-      <c r="M7" s="7" t="n"/>
-      <c r="N7" s="7" t="n"/>
-      <c r="O7" s="7" t="n"/>
-      <c r="P7" s="7" t="n"/>
-      <c r="Q7" s="7" t="n"/>
-      <c r="R7" s="7" t="n"/>
-      <c r="S7" s="7" t="n"/>
-      <c r="T7" s="7" t="n"/>
-      <c r="U7" s="7" t="n"/>
-      <c r="V7" s="7" t="n"/>
-      <c r="W7" s="7" t="n"/>
-      <c r="X7" s="7" t="n"/>
-      <c r="Y7" s="7" t="n"/>
-      <c r="Z7" s="7" t="n"/>
+      <c r="B7" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z7" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -4232,31 +4532,81 @@
           <t>С07</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="7" t="n"/>
-      <c r="L8" s="7" t="n"/>
-      <c r="M8" s="7" t="n"/>
-      <c r="N8" s="7" t="n"/>
-      <c r="O8" s="7" t="n"/>
-      <c r="P8" s="7" t="n"/>
-      <c r="Q8" s="7" t="n"/>
-      <c r="R8" s="7" t="n"/>
-      <c r="S8" s="7" t="n"/>
-      <c r="T8" s="7" t="n"/>
-      <c r="U8" s="7" t="n"/>
-      <c r="V8" s="7" t="n"/>
-      <c r="W8" s="7" t="n"/>
-      <c r="X8" s="7" t="n"/>
-      <c r="Y8" s="7" t="n"/>
-      <c r="Z8" s="7" t="n"/>
+      <c r="B8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z8" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -4264,31 +4614,81 @@
           <t>С08</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
-      <c r="L9" s="7" t="n"/>
-      <c r="M9" s="7" t="n"/>
-      <c r="N9" s="7" t="n"/>
-      <c r="O9" s="7" t="n"/>
-      <c r="P9" s="7" t="n"/>
-      <c r="Q9" s="7" t="n"/>
-      <c r="R9" s="7" t="n"/>
-      <c r="S9" s="7" t="n"/>
-      <c r="T9" s="7" t="n"/>
-      <c r="U9" s="7" t="n"/>
-      <c r="V9" s="7" t="n"/>
-      <c r="W9" s="7" t="n"/>
-      <c r="X9" s="7" t="n"/>
-      <c r="Y9" s="7" t="n"/>
-      <c r="Z9" s="7" t="n"/>
+      <c r="B9" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z9" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -4296,31 +4696,81 @@
           <t>С09</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
-      <c r="N10" s="7" t="n"/>
-      <c r="O10" s="7" t="n"/>
-      <c r="P10" s="7" t="n"/>
-      <c r="Q10" s="7" t="n"/>
-      <c r="R10" s="7" t="n"/>
-      <c r="S10" s="7" t="n"/>
-      <c r="T10" s="7" t="n"/>
-      <c r="U10" s="7" t="n"/>
-      <c r="V10" s="7" t="n"/>
-      <c r="W10" s="7" t="n"/>
-      <c r="X10" s="7" t="n"/>
-      <c r="Y10" s="7" t="n"/>
-      <c r="Z10" s="7" t="n"/>
+      <c r="B10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -4328,31 +4778,81 @@
           <t>С10</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="n"/>
-      <c r="O11" s="7" t="n"/>
-      <c r="P11" s="7" t="n"/>
-      <c r="Q11" s="7" t="n"/>
-      <c r="R11" s="7" t="n"/>
-      <c r="S11" s="7" t="n"/>
-      <c r="T11" s="7" t="n"/>
-      <c r="U11" s="7" t="n"/>
-      <c r="V11" s="7" t="n"/>
-      <c r="W11" s="7" t="n"/>
-      <c r="X11" s="7" t="n"/>
-      <c r="Y11" s="7" t="n"/>
-      <c r="Z11" s="7" t="n"/>
+      <c r="B11" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -4360,31 +4860,81 @@
           <t>С11</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="7" t="n"/>
-      <c r="P12" s="7" t="n"/>
-      <c r="Q12" s="7" t="n"/>
-      <c r="R12" s="7" t="n"/>
-      <c r="S12" s="7" t="n"/>
-      <c r="T12" s="7" t="n"/>
-      <c r="U12" s="7" t="n"/>
-      <c r="V12" s="7" t="n"/>
-      <c r="W12" s="7" t="n"/>
-      <c r="X12" s="7" t="n"/>
-      <c r="Y12" s="7" t="n"/>
-      <c r="Z12" s="7" t="n"/>
+      <c r="B12" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -4392,31 +4942,81 @@
           <t>С12</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="7" t="n"/>
-      <c r="O13" s="7" t="n"/>
-      <c r="P13" s="7" t="n"/>
-      <c r="Q13" s="7" t="n"/>
-      <c r="R13" s="7" t="n"/>
-      <c r="S13" s="7" t="n"/>
-      <c r="T13" s="7" t="n"/>
-      <c r="U13" s="7" t="n"/>
-      <c r="V13" s="7" t="n"/>
-      <c r="W13" s="7" t="n"/>
-      <c r="X13" s="7" t="n"/>
-      <c r="Y13" s="7" t="n"/>
-      <c r="Z13" s="7" t="n"/>
+      <c r="B13" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z13" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -4424,31 +5024,81 @@
           <t>С13</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
-      <c r="L14" s="7" t="n"/>
-      <c r="M14" s="7" t="n"/>
-      <c r="N14" s="7" t="n"/>
-      <c r="O14" s="7" t="n"/>
-      <c r="P14" s="7" t="n"/>
-      <c r="Q14" s="7" t="n"/>
-      <c r="R14" s="7" t="n"/>
-      <c r="S14" s="7" t="n"/>
-      <c r="T14" s="7" t="n"/>
-      <c r="U14" s="7" t="n"/>
-      <c r="V14" s="7" t="n"/>
-      <c r="W14" s="7" t="n"/>
-      <c r="X14" s="7" t="n"/>
-      <c r="Y14" s="7" t="n"/>
-      <c r="Z14" s="7" t="n"/>
+      <c r="B14" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -4456,31 +5106,81 @@
           <t>С14</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
-      <c r="N15" s="7" t="n"/>
-      <c r="O15" s="7" t="n"/>
-      <c r="P15" s="7" t="n"/>
-      <c r="Q15" s="7" t="n"/>
-      <c r="R15" s="7" t="n"/>
-      <c r="S15" s="7" t="n"/>
-      <c r="T15" s="7" t="n"/>
-      <c r="U15" s="7" t="n"/>
-      <c r="V15" s="7" t="n"/>
-      <c r="W15" s="7" t="n"/>
-      <c r="X15" s="7" t="n"/>
-      <c r="Y15" s="7" t="n"/>
-      <c r="Z15" s="7" t="n"/>
+      <c r="B15" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z15" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -4488,31 +5188,81 @@
           <t>С15</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="7" t="n"/>
-      <c r="N16" s="7" t="n"/>
-      <c r="O16" s="7" t="n"/>
-      <c r="P16" s="7" t="n"/>
-      <c r="Q16" s="7" t="n"/>
-      <c r="R16" s="7" t="n"/>
-      <c r="S16" s="7" t="n"/>
-      <c r="T16" s="7" t="n"/>
-      <c r="U16" s="7" t="n"/>
-      <c r="V16" s="7" t="n"/>
-      <c r="W16" s="7" t="n"/>
-      <c r="X16" s="7" t="n"/>
-      <c r="Y16" s="7" t="n"/>
-      <c r="Z16" s="7" t="n"/>
+      <c r="B16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -4520,31 +5270,81 @@
           <t>С16</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="7" t="n"/>
-      <c r="N17" s="7" t="n"/>
-      <c r="O17" s="7" t="n"/>
-      <c r="P17" s="7" t="n"/>
-      <c r="Q17" s="7" t="n"/>
-      <c r="R17" s="7" t="n"/>
-      <c r="S17" s="7" t="n"/>
-      <c r="T17" s="7" t="n"/>
-      <c r="U17" s="7" t="n"/>
-      <c r="V17" s="7" t="n"/>
-      <c r="W17" s="7" t="n"/>
-      <c r="X17" s="7" t="n"/>
-      <c r="Y17" s="7" t="n"/>
-      <c r="Z17" s="7" t="n"/>
+      <c r="B17" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z17" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -4552,31 +5352,81 @@
           <t>С17</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
-      <c r="I18" s="7" t="n"/>
-      <c r="J18" s="7" t="n"/>
-      <c r="K18" s="7" t="n"/>
-      <c r="L18" s="7" t="n"/>
-      <c r="M18" s="7" t="n"/>
-      <c r="N18" s="7" t="n"/>
-      <c r="O18" s="7" t="n"/>
-      <c r="P18" s="7" t="n"/>
-      <c r="Q18" s="7" t="n"/>
-      <c r="R18" s="7" t="n"/>
-      <c r="S18" s="7" t="n"/>
-      <c r="T18" s="7" t="n"/>
-      <c r="U18" s="7" t="n"/>
-      <c r="V18" s="7" t="n"/>
-      <c r="W18" s="7" t="n"/>
-      <c r="X18" s="7" t="n"/>
-      <c r="Y18" s="7" t="n"/>
-      <c r="Z18" s="7" t="n"/>
+      <c r="B18" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -4584,31 +5434,81 @@
           <t>С18</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="7" t="n"/>
-      <c r="N19" s="7" t="n"/>
-      <c r="O19" s="7" t="n"/>
-      <c r="P19" s="7" t="n"/>
-      <c r="Q19" s="7" t="n"/>
-      <c r="R19" s="7" t="n"/>
-      <c r="S19" s="7" t="n"/>
-      <c r="T19" s="7" t="n"/>
-      <c r="U19" s="7" t="n"/>
-      <c r="V19" s="7" t="n"/>
-      <c r="W19" s="7" t="n"/>
-      <c r="X19" s="7" t="n"/>
-      <c r="Y19" s="7" t="n"/>
-      <c r="Z19" s="7" t="n"/>
+      <c r="B19" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -4616,31 +5516,81 @@
           <t>С19</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
-      <c r="L20" s="7" t="n"/>
-      <c r="M20" s="7" t="n"/>
-      <c r="N20" s="7" t="n"/>
-      <c r="O20" s="7" t="n"/>
-      <c r="P20" s="7" t="n"/>
-      <c r="Q20" s="7" t="n"/>
-      <c r="R20" s="7" t="n"/>
-      <c r="S20" s="7" t="n"/>
-      <c r="T20" s="7" t="n"/>
-      <c r="U20" s="7" t="n"/>
-      <c r="V20" s="7" t="n"/>
-      <c r="W20" s="7" t="n"/>
-      <c r="X20" s="7" t="n"/>
-      <c r="Y20" s="7" t="n"/>
-      <c r="Z20" s="7" t="n"/>
+      <c r="B20" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
